--- a/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya porte un verre d'eau. Elle est dans la cuisine, avec papa. Le verre penche. L'eau glisse sur la table. Maya sent ses joues brûlantes. Elle baisse les yeux. Maya dit : je suis gênée. Papa dit : une erreur, ce n'est pas toi. L'erreur, on peut la dire. Maya dit : j'ai versé l'eau. Papa tend un torchon. Maya dit : je veux réparer. Elle essuie la table. Papa aide un peu. Maya relève la tête. Papa dit : merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer.</t>
+          <t>Maya porte un verre d'eau. Elle est dans la cuisine, avec papa. Le verre penche. L'eau glisse sur la table. Maya sent ses joues brûlantes. Elle baisse les yeux. Je suis gênée. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé l'eau. Papa tend un torchon. Je veux réparer. Elle essuie la table. Papa aide un peu. Maya relève la tête. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya porte un verre d'eau. Elle est dans la cuisine, avec papa. Le verre penche. L'eau glisse sur la table. Maya sent ses joues brûlantes. Elle baisse les yeux.
+enfant-f|Je suis gênée.
+papa|Une erreur, ce n'est pas toi. L'erreur, on peut la dire.
+enfant-f|J'ai versé l'eau. Papa tend un torchon.
+enfant-f|Je veux réparer. Elle essuie la table. Papa aide un peu.
+narrateur|Maya relève la tête.
+papa|Merci d'avoir dit. Être gêné, on le dit.
+narrateur|Puis on peut réparer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a versé l'eau. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a nommé : gêné. L'erreur n'est pas Maya. Elle a pu réparer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La table est sèche. Maya pose le torchon. Papa lui sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Puis on peut réparer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Maya a versé l'eau. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Maya a nommé : gêné. L'erreur n'est pas Maya. Elle a pu réparer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|La table est sèche. Maya pose le torchon. Papa lui sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Être gêné</t>
+          <t>Sarah est gênée</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah porte un verre d'eau. L'eau glisse. Elle dit qu'elle est gênée. Elle répare avec un torchon.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya porte un verre d'eau. Elle est dans la cuisine, avec papa. Le verre penche. L'eau glisse sur la table. Maya sent ses joues brûlantes. Elle baisse les yeux. Je suis gênée. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé l'eau. Papa tend un torchon. Je veux réparer. Elle essuie la table. Papa aide un peu. Maya relève la tête. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer.</t>
+          <t>La fenêtre de la cuisine est toute embuée. Un petit nuage d'eau tient sur la vitre. Ça sent la soupe, tout chaud. La casserole chante un tout petit chant. La table en bois a des veines claires. Un torchon à carreaux pend près de l'évier. Une cuillère en bois repose près de la casserole. Le carrelage est un peu tiède sous les pieds. Sarah, tu peux porter le verre d'eau ? Tout doux, jusqu'à la table. Oui, papa. Je le porte. En ce moment, Sarah marche vers la table. Le verre est frais entre ses mains. Le verre penche un peu. L'eau glisse sur la table. Une petite flaque brille sur le bois. Sarah sent ses joues brûlantes. Elle baisse les yeux. Je suis gênée. Tu es gênée. Je t'écoute. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé l'eau. Merci d'avoir dit. Voici le torchon. Je veux réparer. Sarah essuie la table. Le bois redevient sec, tout doux. J'aide un peu, à côté de toi. Papa essuie un coin. Sarah relève la tête. Être gêné, on le dit. Puis on peut réparer. J'ai dit. J'ai réparé. Bravo, Sarah. C'est du bon travail. Tes joues sont moins chaudes, maintenant ? Oui, papa. L'erreur n'est pas toi. La soupe chante encore, tout bas. La fenêtre reste un peu embuée. On dessine un soleil sur la buée ? Un petit rond, tout doux. Oui. Puis on essuie le doigt.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maya porte un verre d'eau. Elle est dans la cuisine, avec papa. Le verre penche. L'eau glisse sur la table. Maya sent ses joues brûlantes. Elle baisse les yeux.
+          <t>narrateur|La fenêtre de la cuisine est toute embuée.
+narrateur|Un petit nuage d'eau tient sur la vitre.
+narrateur|Ça sent la soupe, tout chaud.
+narrateur|La casserole chante un tout petit chant.
+narrateur|La table en bois a des veines claires.
+narrateur|Un torchon à carreaux pend près de l'évier.
+narrateur|Une cuillère en bois repose près de la casserole.
+narrateur|Le carrelage est un peu tiède sous les pieds.
+papa|Sarah, tu peux porter le verre d'eau ?
+papa|Tout doux, jusqu'à la table.
+enfant-f|Oui, papa.
+enfant-f|Je le porte.
+narrateur|En ce moment, Sarah marche vers la table.
+narrateur|Le verre est frais entre ses mains.
+narrateur|Le verre penche un peu.
+narrateur|L'eau glisse sur la table.
+narrateur|Une petite flaque brille sur le bois.
+narrateur|Sarah sent ses joues brûlantes.
+narrateur|Elle baisse les yeux.
 enfant-f|Je suis gênée.
-papa|Une erreur, ce n'est pas toi. L'erreur, on peut la dire.
-enfant-f|J'ai versé l'eau. Papa tend un torchon.
-enfant-f|Je veux réparer. Elle essuie la table. Papa aide un peu.
-narrateur|Maya relève la tête.
-papa|Merci d'avoir dit. Être gêné, on le dit.
-narrateur|Puis on peut réparer.</t>
+papa|Tu es gênée.
+papa|Je t'écoute.
+papa|Une erreur, ce n'est pas toi.
+papa|L'erreur, on peut la dire.
+enfant-f|J'ai versé l'eau.
+papa|Merci d'avoir dit.
+papa|Voici le torchon.
+enfant-f|Je veux réparer.
+narrateur|Sarah essuie la table.
+narrateur|Le bois redevient sec, tout doux.
+papa|J'aide un peu, à côté de toi.
+narrateur|Papa essuie un coin.
+narrateur|Sarah relève la tête.
+papa|Être gêné, on le dit.
+papa|Puis on peut réparer.
+enfant-f|J'ai dit.
+enfant-f|J'ai réparé.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+papa|Tes joues sont moins chaudes, maintenant ?
+enfant-f|Oui, papa.
+papa|L'erreur n'est pas toi.
+narrateur|La soupe chante encore, tout bas.
+narrateur|La fenêtre reste un peu embuée.
+papa|On dessine un soleil sur la buée ?
+enfant-f|Un petit rond, tout doux.
+papa|Oui.
+papa|Puis on essuie le doigt.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1347,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maya a versé l'eau. Que fait-elle ?</t>
+          <t>Sarah a versé l'eau. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1555,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maya a versé l'eau. Que fait-elle ?</t>
+          <t>narrateur|Sarah a versé l'eau.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya a nommé : gêné. L'erreur n'est pas Maya. Elle a pu réparer.</t>
+          <t>Sarah a nommé : gêné. L'erreur n'est pas Sarah. Elle a pu réparer. Je suis gênée. J'ai versé. J'ai réparé. Oui. Tu as dit l'erreur. Bravo. C'est du bon travail. Le torchon est un peu humide. On le pose près de l'évier ? Oui. La table est sèche. Être gêné, on le dit. Puis on répare. La cuillère en bois n'a pas bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1728,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya a nommé : gêné. L'erreur n'est pas Maya. Elle a pu réparer.</t>
+          <t>narrateur|Sarah a nommé : gêné.
+narrateur|L'erreur n'est pas Sarah.
+narrateur|Elle a pu réparer.
+enfant-f|Je suis gênée.
+enfant-f|J'ai versé.
+enfant-f|J'ai réparé.
+papa|Oui.
+papa|Tu as dit l'erreur.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le torchon est un peu humide.
+papa|On le pose près de l'évier ?
+enfant-f|Oui.
+enfant-f|La table est sèche.
+papa|Être gêné, on le dit.
+papa|Puis on répare.
+narrateur|La cuillère en bois n'a pas bougé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La table est sèche. Maya pose le torchon. Papa lui sourit.</t>
+          <t>La table est sèche. Sarah pose le torchon. Tu poses le verre, tout droit ? Oui. Tout doux. Merci d'avoir dit. L'erreur n'est pas toi. J'étais gênée. Et tu as réparé. Bravo. La soupe sent encore le légume. On sert la soupe, maintenant ? Oui, papa. Un peu de buée reste sur la vitre. Le petit rond s'efface tout seul. La soupe est prête. Je m'assois. Tu as dit l'erreur. Tu as réparé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1908,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La table est sèche. Maya pose le torchon. Papa lui sourit.</t>
+          <t>narrateur|La table est sèche.
+narrateur|Sarah pose le torchon.
+papa|Tu poses le verre, tout droit ?
+enfant-f|Oui.
+enfant-f|Tout doux.
+papa|Merci d'avoir dit.
+papa|L'erreur n'est pas toi.
+enfant-f|J'étais gênée.
+papa|Et tu as réparé.
+papa|Bravo.
+narrateur|La soupe sent encore le légume.
+papa|On sert la soupe, maintenant ?
+enfant-f|Oui, papa.
+narrateur|Un peu de buée reste sur la vitre.
+narrateur|Le petit rond s'efface tout seul.
+papa|La soupe est prête.
+enfant-f|Je m'assois.
+papa|Tu as dit l'erreur.
+papa|Tu as réparé.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Sarah. Tu as fait du bon travail. La table est sèche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2094,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais gênée.
+enfant-f|J'ai dit.
+enfant-f|J'ai réparé.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+narrateur|La table est sèche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La fenêtre de la cuisine est toute embuée. Un petit nuage d'eau tient sur la vitre. Ça sent la soupe, tout chaud. La casserole chante un tout petit chant. La table en bois a des veines claires. Un torchon à carreaux pend près de l'évier. Une cuillère en bois repose près de la casserole. Le carrelage est un peu tiède sous les pieds. Sarah, tu peux porter le verre d'eau ? Tout doux, jusqu'à la table. Oui, papa. Je le porte. En ce moment, Sarah marche vers la table. Le verre est frais entre ses mains. Le verre penche un peu. L'eau glisse sur la table. Une petite flaque brille sur le bois. Sarah sent ses joues brûlantes. Elle baisse les yeux. Je suis gênée. Tu es gênée. Je t'écoute. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé l'eau. Merci d'avoir dit. Voici le torchon. Je veux réparer. Sarah essuie la table. Le bois redevient sec, tout doux. J'aide un peu, à côté de toi. Papa essuie un coin. Sarah relève la tête. Être gêné, on le dit. Puis on peut réparer. J'ai dit. J'ai réparé. Bravo, Sarah. C'est du bon travail. Tes joues sont moins chaudes, maintenant ? Oui, papa. L'erreur n'est pas toi. La soupe chante encore, tout bas. La fenêtre reste un peu embuée. On dessine un soleil sur la buée ? Un petit rond, tout doux. Oui. Puis on essuie le doigt.</t>
+          <t>La fenêtre de la cuisine est toute embuée. Un petit nuage d'eau tient sur la vitre. Ça sent la soupe, tout chaud. La casserole chante un tout petit chant. La table en bois a des veines claires. Un torchon à carreaux pend près de l'évier. Une cuillère en bois repose près de la casserole. Le carrelage est un peu tiède sous les pieds. Sarah, tu peux porter le verre d'eau ? Tout doux, jusqu'à la table. Oui, papa. Je le porte. En ce moment, Sarah marche vers la table. Le verre est frais entre ses mains. Le verre penche un peu. L'eau glisse sur la table. Une petite flaque brille sur le bois. Sarah sent ses joues brûlantes. Elle baisse les yeux. Je suis gênée. Tu es gênée. Je t'écoute. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé l'eau. Merci d'avoir dit. Voici le torchon. Je veux réparer. Sarah essuie la table. Le bois redevient sec, tout doux. J'aide un peu, à côté de toi. Papa essuie un coin. Sarah relève la tête. Être gêné, on le dit. Puis on peut réparer. J'ai dit. J'ai réparé. Bravo, Sarah. Tes joues sont moins chaudes, maintenant ? Oui, papa. L'erreur n'est pas toi. La soupe chante encore, tout bas. La fenêtre reste un peu embuée. On dessine un soleil sur la buée ? Un petit rond, tout doux. Oui. Puis on essuie le doigt.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya porte un verre d'eau. Elle est dans la cuisine, avec papa. Le verre penche. L'eau glisse sur la table. Maya sent ses joues brûlantes. Elle baisse les yeux. Maya dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;e. Papa dit : une erreur, ce n'est pas toi. L'erreur, on peut la dire. Maya dit : j'ai versé l'eau. Papa tend un torchon. Maya dit : je veux réparer. Elle essuie la table. Papa aide un peu. Maya relève la tête. Papa dit : merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fenêtre de la cuisine est toute embuée. Un petit nuage d'eau tient sur la vitre. Ça sent la soupe, tout chaud. La casserole chante un tout petit chant. La table en bois a des veines claires. Un torchon à carreaux pend près de l'évier. Une cuillère en bois repose près de la casserole. Le carrelage est un peu tiède sous les pieds. Sarah, tu peux porter le verre d'eau ? Tout doux, jusqu'à la table. Oui, papa. Je le porte. En ce moment, Sarah marche vers la table. Le verre est frais entre ses mains. Le verre penche un peu. L'eau glisse sur la table. Une petite flaque brille sur le bois. Sarah sent ses joues brûlantes. Elle baisse les yeux. Je suis gênée. Tu es gênée. Je t'écoute. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé l'eau. Merci d'avoir dit. Voici le torchon. Je veux réparer. Sarah essuie la table. Le bois redevient sec, tout doux. J'aide un peu, à côté de toi. Papa essuie un coin. Sarah relève la tête. Être gêné, on le dit. Puis on peut réparer. J'ai dit. J'ai réparé. Bravo, Sarah. Tes joues sont moins chaudes, maintenant ? Oui, papa. L'erreur n'est pas toi. La soupe chante encore, tout bas. La fenêtre reste un peu embuée. On dessine un soleil sur la buée ? Un petit rond, tout doux. Oui. Puis on essuie le doigt.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1362,7 +1362,6 @@
 enfant-f|J'ai dit.
 enfant-f|J'ai réparé.
 papa|Bravo, Sarah.
-papa|C'est du bon travail.
 papa|Tes joues sont moins chaudes, maintenant ?
 enfant-f|Oui, papa.
 papa|L'erreur n'est pas toi.
@@ -1374,7 +1373,6 @@
 papa|Puis on essuie le doigt.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1404,7 +1402,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya a versé l'eau. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a versé l'eau. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1559,7 +1557,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1584,12 +1581,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a nommé : gêné. L'erreur n'est pas Sarah. Elle a pu réparer. Je suis gênée. J'ai versé. J'ai réparé. Oui. Tu as dit l'erreur. Bravo. C'est du bon travail. Le torchon est un peu humide. On le pose près de l'évier ? Oui. La table est sèche. Être gêné, on le dit. Puis on répare. La cuillère en bois n'a pas bougé.</t>
+          <t>Sarah a nommé : gêné. L'erreur n'est pas Sarah. Elle a pu réparer. Je suis gênée. J'ai versé. J'ai réparé. Oui. Tu as dit l'erreur. Bravo. Le torchon est un peu humide. On le pose près de l'évier ? Oui. La table est sèche. Être gêné, on le dit. Puis on répare. La cuillère en bois n'a pas bougé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maya a nommé : &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;. L'erreur n'est pas Maya. Elle a pu réparer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a nommé : gêné. L'erreur n'est pas Sarah. Elle a pu réparer. Je suis gênée. J'ai versé. J'ai réparé. Oui. Tu as dit l'erreur. Bravo. Le torchon est un peu humide. On le pose près de l'évier ? Oui. La table est sèche. Être gêné, on le dit. Puis on répare. La cuillère en bois n'a pas bougé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,7 +1734,6 @@
 papa|Oui.
 papa|Tu as dit l'erreur.
 papa|Bravo.
-papa|C'est du bon travail.
 narrateur|Le torchon est un peu humide.
 papa|On le pose près de l'évier ?
 enfant-f|Oui.
@@ -1747,7 +1743,6 @@
 narrateur|La cuillère en bois n'a pas bougé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,7 +1772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La table est sèche. Maya pose le torchon. Papa lui sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La table est sèche. Sarah pose le torchon. Tu poses le verre, tout droit ? Oui. Tout doux. Merci d'avoir dit. L'erreur n'est pas toi. J'étais gênée. Et tu as réparé. Bravo. La soupe sent encore le légume. On sert la soupe, maintenant ? Oui, papa. Un peu de buée reste sur la vitre. Le petit rond s'efface tout seul. La soupe est prête. Je m'assois. Tu as dit l'erreur. Tu as réparé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1929,7 +1924,6 @@
 papa|Tu as réparé.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1954,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Sarah. Tu as fait du bon travail. La table est sèche. L'histoire est finie.</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Sarah. La table est sèche.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais gênée. J'ai dit. J'ai réparé. Bravo, Sarah. La table est sèche.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,12 +2092,9 @@
 enfant-f|J'ai dit.
 enfant-f|J'ai réparé.
 papa|Bravo, Sarah.
-papa|Tu as fait du bon travail.
-narrateur|La table est sèche.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La table est sèche.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
